--- a/2025-MP CEN-24083.xlsx
+++ b/2025-MP CEN-24083.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hesalinas\OneDrive - Swiss Medical S.A (1)\000 Auditorías Laboratorios GENERAL\Laboratorio Catamarca\2025\Centrifugas 12.03.2025\Piso 1 12.03.2025\CEN-24083\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hesalinas\Documents\SAP\TERUMO\Mondis\Centrifugas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5315681A-4EF8-4E17-8B44-A31F60AC97EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Desarrollo" sheetId="4" r:id="rId1"/>
@@ -23,6 +24,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -351,7 +355,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1311,7 +1315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -1567,22 +1571,476 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1608,458 +2066,40 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2192,14 +2232,63 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E153A9B-61F6-40BD-ACA1-B8DA50FEBB5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7248525" y="1771650"/>
+          <a:ext cx="1285875" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2237,9 +2326,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2274,7 +2363,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2309,7 +2398,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2482,7 +2571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2495,42 +2584,42 @@
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="78" t="s">
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="79"/>
+      <c r="J1" s="172"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35"/>
       <c r="B2" s="36"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="174"/>
     </row>
     <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="35"/>
       <c r="B3" s="36"/>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="178" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="179"/>
       <c r="I3" s="46" t="s">
         <v>3</v>
       </c>
@@ -2541,126 +2630,126 @@
     <row r="4" spans="1:10" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
       <c r="B4" s="36"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="86"/>
+      <c r="C4" s="178"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="179"/>
       <c r="I4" s="47" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110" t="s">
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="111"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="134"/>
       <c r="G5" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="105" t="s">
+      <c r="H5" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="134"/>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="109"/>
+      <c r="A6" s="162"/>
+      <c r="B6" s="131"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="132"/>
       <c r="G6" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="99" t="s">
+      <c r="H6" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="100"/>
-      <c r="J6" s="102"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="141"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="155" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="128"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="108" t="s">
+      <c r="B7" s="156"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="108"/>
-      <c r="F7" s="109"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="132"/>
       <c r="G7" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="124" t="s">
+      <c r="H7" s="150" t="s">
         <v>105</v>
       </c>
-      <c r="I7" s="125"/>
-      <c r="J7" s="126"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="152"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="130"/>
-      <c r="B8" s="131"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="109"/>
+      <c r="A8" s="158"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="132"/>
       <c r="G8" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="124">
+      <c r="H8" s="150">
         <v>45728</v>
       </c>
-      <c r="I8" s="91"/>
-      <c r="J8" s="92"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="154"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="135"/>
-      <c r="B9" s="136"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="137"/>
+      <c r="A9" s="163"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="165"/>
       <c r="G9" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="183">
         <v>9226480</v>
       </c>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="154"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="138"/>
-      <c r="B10" s="139"/>
-      <c r="C10" s="139"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="139"/>
-      <c r="F10" s="140"/>
+      <c r="A10" s="166"/>
+      <c r="B10" s="167"/>
+      <c r="C10" s="167"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="168"/>
       <c r="G10" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="93" t="s">
+      <c r="H10" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="94"/>
-      <c r="J10" s="95"/>
+      <c r="I10" s="185"/>
+      <c r="J10" s="186"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="122" t="s">
+      <c r="A11" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="123"/>
+      <c r="B11" s="149"/>
       <c r="C11" s="65" t="s">
         <v>18</v>
       </c>
@@ -2670,19 +2759,19 @@
       <c r="E11" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="141" t="s">
+      <c r="F11" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="142"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="196"/>
+      <c r="I11" s="197"/>
+      <c r="J11" s="198"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="100"/>
+      <c r="B12" s="140"/>
       <c r="C12" s="64" t="s">
         <v>23</v>
       </c>
@@ -2692,19 +2781,19 @@
       <c r="E12" s="64">
         <v>2982052</v>
       </c>
-      <c r="F12" s="101">
+      <c r="F12" s="187">
         <v>45415</v>
       </c>
-      <c r="G12" s="102"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="118" t="s">
+      <c r="G12" s="141"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="200"/>
+      <c r="J12" s="201"/>
+    </row>
+    <row r="13" spans="1:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="119"/>
+      <c r="B13" s="145"/>
       <c r="C13" s="66" t="s">
         <v>26</v>
       </c>
@@ -2714,34 +2803,34 @@
       <c r="E13" s="19">
         <v>161118070</v>
       </c>
-      <c r="F13" s="103">
+      <c r="F13" s="188">
         <v>45435</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
+      <c r="G13" s="189"/>
+      <c r="H13" s="202"/>
+      <c r="I13" s="203"/>
+      <c r="J13" s="204"/>
     </row>
     <row r="14" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="120"/>
-      <c r="B14" s="121"/>
+      <c r="A14" s="146"/>
+      <c r="B14" s="147"/>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="117"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="143"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="112"/>
-      <c r="B15" s="113"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="136"/>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="115"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="138"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2759,29 +2848,29 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="193" t="s">
+      <c r="A17" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="194"/>
-      <c r="C17" s="194"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="194"/>
-      <c r="G17" s="195"/>
+      <c r="B17" s="80"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="81"/>
       <c r="H17" s="4"/>
       <c r="I17" s="5"/>
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="184" t="s">
+      <c r="A18" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="186"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="72"/>
       <c r="H18" s="28" t="s">
         <v>30</v>
       </c>
@@ -2789,127 +2878,127 @@
       <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="190" t="s">
+      <c r="A19" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="191"/>
-      <c r="G19" s="192"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="78"/>
       <c r="H19" s="26"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="190" t="s">
+      <c r="A20" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="191"/>
-      <c r="C20" s="191"/>
-      <c r="D20" s="191"/>
-      <c r="E20" s="191"/>
-      <c r="F20" s="191"/>
-      <c r="G20" s="192"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="78"/>
       <c r="H20" s="26"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="181" t="s">
+      <c r="A21" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="182"/>
-      <c r="C21" s="182"/>
-      <c r="D21" s="182"/>
-      <c r="E21" s="182"/>
-      <c r="F21" s="182"/>
-      <c r="G21" s="183"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="89"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
+      <c r="A22" s="182"/>
+      <c r="B22" s="182"/>
+      <c r="C22" s="182"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="182"/>
+      <c r="F22" s="182"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="182"/>
+      <c r="I22" s="182"/>
+      <c r="J22" s="182"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="187" t="s">
+      <c r="A23" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="188"/>
-      <c r="C23" s="188"/>
-      <c r="D23" s="188"/>
-      <c r="E23" s="188"/>
-      <c r="F23" s="188"/>
-      <c r="G23" s="189"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="75"/>
       <c r="H23" s="7"/>
       <c r="I23" s="8"/>
       <c r="J23" s="9"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="89"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
+      <c r="A24" s="182"/>
+      <c r="B24" s="182"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+      <c r="E24" s="182"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="182"/>
+      <c r="I24" s="182"/>
+      <c r="J24" s="182"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="167" t="s">
+      <c r="A25" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="152" t="s">
+      <c r="B25" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="177"/>
-      <c r="B26" s="69" t="s">
+      <c r="A26" s="102"/>
+      <c r="B26" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="68"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="174" t="s">
+      <c r="B27" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="175"/>
-      <c r="D27" s="175"/>
-      <c r="E27" s="175"/>
-      <c r="F27" s="175"/>
-      <c r="G27" s="176"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="101"/>
       <c r="H27" s="23" t="s">
         <v>40</v>
       </c>
@@ -2920,14 +3009,14 @@
       <c r="A28" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="98"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="86"/>
       <c r="H28" s="23" t="s">
         <v>40</v>
       </c>
@@ -2938,14 +3027,14 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="98"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="86"/>
       <c r="H29" s="23" t="s">
         <v>40</v>
       </c>
@@ -2956,14 +3045,14 @@
       <c r="A30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="97"/>
-      <c r="G30" s="98"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="86"/>
       <c r="H30" s="23" t="s">
         <v>40</v>
       </c>
@@ -2974,14 +3063,14 @@
       <c r="A31" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="98"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="86"/>
       <c r="H31" s="23" t="s">
         <v>49</v>
       </c>
@@ -2992,14 +3081,14 @@
       <c r="A32" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="98"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="86"/>
       <c r="H32" s="23" t="s">
         <v>40</v>
       </c>
@@ -3010,14 +3099,14 @@
       <c r="A33" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="96" t="s">
+      <c r="B33" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="98"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="86"/>
       <c r="H33" s="23" t="s">
         <v>40</v>
       </c>
@@ -3028,14 +3117,14 @@
       <c r="A34" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="96" t="s">
+      <c r="B34" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="97"/>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="98"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="86"/>
       <c r="H34" s="23" t="s">
         <v>40</v>
       </c>
@@ -3046,14 +3135,14 @@
       <c r="A35" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="97"/>
-      <c r="D35" s="97"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
-      <c r="G35" s="98"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="86"/>
       <c r="H35" s="23" t="s">
         <v>40</v>
       </c>
@@ -3064,14 +3153,14 @@
       <c r="A36" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B36" s="159" t="s">
+      <c r="B36" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="160"/>
-      <c r="D36" s="160"/>
-      <c r="E36" s="160"/>
-      <c r="F36" s="160"/>
-      <c r="G36" s="161"/>
+      <c r="C36" s="123"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="123"/>
+      <c r="G36" s="124"/>
       <c r="H36" s="23" t="s">
         <v>40</v>
       </c>
@@ -3082,14 +3171,14 @@
       <c r="A37" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="97"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="98"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="86"/>
       <c r="H37" s="23" t="s">
         <v>40</v>
       </c>
@@ -3100,14 +3189,14 @@
       <c r="A38" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="96" t="s">
+      <c r="B38" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="86"/>
       <c r="H38" s="23" t="s">
         <v>40</v>
       </c>
@@ -3118,14 +3207,14 @@
       <c r="A39" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="96" t="s">
+      <c r="B39" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="97"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="97"/>
-      <c r="G39" s="98"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="86"/>
       <c r="H39" s="23" t="s">
         <v>49</v>
       </c>
@@ -3136,14 +3225,14 @@
       <c r="A40" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="155" t="s">
+      <c r="B40" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="156"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="157"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="120"/>
       <c r="H40" s="23" t="s">
         <v>49</v>
       </c>
@@ -3151,29 +3240,29 @@
       <c r="J40" s="27"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="89"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
+      <c r="A41" s="182"/>
+      <c r="B41" s="182"/>
+      <c r="C41" s="182"/>
+      <c r="D41" s="182"/>
+      <c r="E41" s="182"/>
+      <c r="F41" s="182"/>
+      <c r="G41" s="182"/>
+      <c r="H41" s="182"/>
+      <c r="I41" s="182"/>
+      <c r="J41" s="182"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="149" t="s">
+      <c r="B42" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="150"/>
-      <c r="D42" s="150"/>
-      <c r="E42" s="150"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="151"/>
+      <c r="C42" s="114"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="114"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="115"/>
       <c r="H42" s="13" t="s">
         <v>70</v>
       </c>
@@ -3188,14 +3277,14 @@
       <c r="A43" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="146" t="s">
+      <c r="B43" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="147"/>
-      <c r="D43" s="147"/>
-      <c r="E43" s="147"/>
-      <c r="F43" s="147"/>
-      <c r="G43" s="148"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="94"/>
+      <c r="F43" s="94"/>
+      <c r="G43" s="95"/>
       <c r="H43" s="54" t="s">
         <v>49</v>
       </c>
@@ -3208,14 +3297,14 @@
     </row>
     <row r="44" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="37"/>
-      <c r="B44" s="169" t="s">
+      <c r="B44" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="170"/>
-      <c r="D44" s="170"/>
-      <c r="E44" s="170"/>
-      <c r="F44" s="170"/>
-      <c r="G44" s="171"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="91"/>
+      <c r="F44" s="91"/>
+      <c r="G44" s="92"/>
       <c r="H44" s="54"/>
       <c r="I44" s="54"/>
       <c r="J44" s="57"/>
@@ -3224,14 +3313,14 @@
       <c r="A45" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="146" t="s">
+      <c r="B45" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="147"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="148"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="95"/>
       <c r="H45" s="55">
         <v>60</v>
       </c>
@@ -3244,14 +3333,14 @@
     </row>
     <row r="46" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15"/>
-      <c r="B46" s="165" t="s">
+      <c r="B46" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="165"/>
-      <c r="D46" s="165"/>
-      <c r="E46" s="165"/>
-      <c r="F46" s="165"/>
-      <c r="G46" s="166"/>
+      <c r="C46" s="106"/>
+      <c r="D46" s="106"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="107"/>
       <c r="H46" s="55" t="s">
         <v>80</v>
       </c>
@@ -3262,14 +3351,14 @@
       <c r="A47" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B47" s="146" t="s">
+      <c r="B47" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="147"/>
-      <c r="D47" s="147"/>
-      <c r="E47" s="147"/>
-      <c r="F47" s="147"/>
-      <c r="G47" s="173"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="97"/>
       <c r="H47" s="55"/>
       <c r="I47" s="55"/>
       <c r="J47" s="58"/>
@@ -3324,14 +3413,14 @@
     </row>
     <row r="51" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
-      <c r="B51" s="165" t="s">
+      <c r="B51" s="106" t="s">
         <v>83</v>
       </c>
-      <c r="C51" s="165"/>
-      <c r="D51" s="165"/>
-      <c r="E51" s="165"/>
-      <c r="F51" s="165"/>
-      <c r="G51" s="166"/>
+      <c r="C51" s="106"/>
+      <c r="D51" s="106"/>
+      <c r="E51" s="106"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="107"/>
       <c r="H51" s="56" t="s">
         <v>84</v>
       </c>
@@ -3339,7 +3428,7 @@
       <c r="J51" s="59"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="167" t="s">
+      <c r="A52" s="82" t="s">
         <v>85</v>
       </c>
       <c r="B52" s="41"/>
@@ -3350,36 +3439,36 @@
       <c r="E52" s="42"/>
       <c r="F52" s="42"/>
       <c r="G52" s="43"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="67"/>
-      <c r="J52" s="67"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="111"/>
+      <c r="J52" s="111"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="172"/>
-      <c r="B53" s="69" t="s">
+      <c r="A53" s="96"/>
+      <c r="B53" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="71"/>
-      <c r="H53" s="68"/>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="89"/>
+      <c r="H53" s="112"/>
+      <c r="I53" s="112"/>
+      <c r="J53" s="112"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B54" s="162" t="s">
+      <c r="B54" s="125" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="163"/>
-      <c r="D54" s="163"/>
-      <c r="E54" s="163"/>
-      <c r="F54" s="163"/>
-      <c r="G54" s="164"/>
+      <c r="C54" s="126"/>
+      <c r="D54" s="126"/>
+      <c r="E54" s="126"/>
+      <c r="F54" s="126"/>
+      <c r="G54" s="127"/>
       <c r="H54" s="17" t="s">
         <v>40</v>
       </c>
@@ -3390,14 +3479,14 @@
       <c r="A55" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="178" t="s">
+      <c r="B55" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="179"/>
-      <c r="D55" s="179"/>
-      <c r="E55" s="179"/>
-      <c r="F55" s="179"/>
-      <c r="G55" s="180"/>
+      <c r="C55" s="104"/>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="105"/>
       <c r="H55" s="17" t="s">
         <v>40</v>
       </c>
@@ -3408,14 +3497,14 @@
       <c r="A56" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="72" t="s">
+      <c r="B56" s="190" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="73"/>
-      <c r="D56" s="73"/>
-      <c r="E56" s="73"/>
-      <c r="F56" s="73"/>
-      <c r="G56" s="74"/>
+      <c r="C56" s="191"/>
+      <c r="D56" s="191"/>
+      <c r="E56" s="191"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="192"/>
       <c r="H56" s="17" t="s">
         <v>40</v>
       </c>
@@ -3426,14 +3515,14 @@
       <c r="A57" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="72" t="s">
+      <c r="B57" s="190" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="74"/>
+      <c r="C57" s="191"/>
+      <c r="D57" s="191"/>
+      <c r="E57" s="191"/>
+      <c r="F57" s="191"/>
+      <c r="G57" s="192"/>
       <c r="H57" s="17" t="s">
         <v>49</v>
       </c>
@@ -3444,14 +3533,14 @@
       <c r="A58" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B58" s="75" t="s">
+      <c r="B58" s="193" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="73"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="76"/>
+      <c r="C58" s="191"/>
+      <c r="D58" s="191"/>
+      <c r="E58" s="191"/>
+      <c r="F58" s="191"/>
+      <c r="G58" s="194"/>
       <c r="H58" s="17" t="s">
         <v>40</v>
       </c>
@@ -3462,14 +3551,14 @@
       <c r="A59" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="B59" s="158" t="s">
+      <c r="B59" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="158"/>
-      <c r="D59" s="158"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
+      <c r="C59" s="121"/>
+      <c r="D59" s="121"/>
+      <c r="E59" s="121"/>
+      <c r="F59" s="121"/>
+      <c r="G59" s="121"/>
       <c r="H59" s="40" t="s">
         <v>40</v>
       </c>
@@ -3477,47 +3566,47 @@
       <c r="J59" s="40"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="167" t="s">
+      <c r="A60" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="B60" s="153" t="s">
+      <c r="B60" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="C60" s="153"/>
-      <c r="D60" s="153"/>
-      <c r="E60" s="153"/>
-      <c r="F60" s="153"/>
-      <c r="G60" s="153"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
+      <c r="C60" s="98"/>
+      <c r="D60" s="98"/>
+      <c r="E60" s="98"/>
+      <c r="F60" s="98"/>
+      <c r="G60" s="98"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="168"/>
-      <c r="B61" s="69" t="s">
+      <c r="A61" s="83"/>
+      <c r="B61" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="77"/>
-      <c r="I61" s="77"/>
-      <c r="J61" s="77"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="195"/>
+      <c r="I61" s="195"/>
+      <c r="J61" s="195"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="B62" s="143" t="s">
+      <c r="B62" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="144"/>
-      <c r="D62" s="144"/>
-      <c r="E62" s="144"/>
-      <c r="F62" s="144"/>
-      <c r="G62" s="145"/>
+      <c r="C62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="110"/>
       <c r="H62" s="60" t="s">
         <v>40</v>
       </c>
@@ -3527,26 +3616,48 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="78">
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="C3:H4"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="D5:F6"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="B62:G62"/>
     <mergeCell ref="H25:H26"/>
     <mergeCell ref="I25:I26"/>
@@ -3563,48 +3674,26 @@
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B54:G54"/>
     <mergeCell ref="B46:G46"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="D5:F6"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="C3:H4"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="I60:I61"/>
-    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H56">
@@ -3660,11 +3749,12 @@
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3676,11 +3766,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="2df84070-181a-4eed-94fc-4bdaa3a04388" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3937,27 +4028,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="2df84070-181a-4eed-94fc-4bdaa3a04388" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88779F27-9C33-4B60-A317-458611D88A22}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536D2E46-E2CA-4A08-9E8C-A4A8B61D3375}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2df84070-181a-4eed-94fc-4bdaa3a04388"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3681945f-a55f-4d63-9244-9615a0ae9a74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3982,9 +4063,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536D2E46-E2CA-4A08-9E8C-A4A8B61D3375}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88779F27-9C33-4B60-A317-458611D88A22}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2df84070-181a-4eed-94fc-4bdaa3a04388"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="3681945f-a55f-4d63-9244-9615a0ae9a74"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>